--- a/pages/Sprint_Points_Women.xlsx
+++ b/pages/Sprint_Points_Women.xlsx
@@ -1093,13 +1093,13 @@
     <t>30 Jul 2022</t>
   </si>
   <si>
-    <t>UCI World Championships</t>
-  </si>
-  <si>
-    <t>Nations' Cup</t>
-  </si>
-  <si>
-    <t>Continental Championships</t>
+    <t>WCh</t>
+  </si>
+  <si>
+    <t>NCp</t>
+  </si>
+  <si>
+    <t>CCh</t>
   </si>
   <si>
     <t>TCL General Ranking</t>
@@ -1108,13 +1108,13 @@
     <t>TCL Round Ranking</t>
   </si>
   <si>
-    <t>National Championships</t>
-  </si>
-  <si>
-    <t>Class 1</t>
-  </si>
-  <si>
-    <t>Class 2</t>
+    <t>NCh</t>
+  </si>
+  <si>
+    <t>CL1</t>
+  </si>
+  <si>
+    <t>CL2</t>
   </si>
   <si>
     <t>National</t>

--- a/pages/Sprint_Points_Women.xlsx
+++ b/pages/Sprint_Points_Women.xlsx
@@ -301,7 +301,7 @@
     <t>CAPOBIANCHI Giada</t>
   </si>
   <si>
-    <t>WANG Sin Ting</t>
+    <t>王WANG 歆婷sin Ting</t>
   </si>
   <si>
     <t>GOLUBKOVA Yuliya (ATT)</t>

--- a/pages/Sprint_Points_Women.xlsx
+++ b/pages/Sprint_Points_Women.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>19 May 2023</t>
+          <t>20 May 2023</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -26498,7 +26498,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -26602,7 +26602,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -28682,7 +28682,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -29618,7 +29618,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>15 Dec 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -30762,7 +30762,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -31594,7 +31594,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>19 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -32738,7 +32738,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -32790,7 +32790,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -32894,7 +32894,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -33102,7 +33102,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -33154,7 +33154,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -33362,7 +33362,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -33414,7 +33414,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -35338,7 +35338,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -35390,7 +35390,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -35598,7 +35598,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -36222,7 +36222,7 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -36690,7 +36690,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -36794,7 +36794,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -37054,7 +37054,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -37366,7 +37366,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -38250,7 +38250,7 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -38874,7 +38874,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -39186,7 +39186,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>15 Dec 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -40746,7 +40746,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -40798,7 +40798,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -41578,7 +41578,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -42358,7 +42358,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>19 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
